--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-05-29_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-05-29_v3_final.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekapitulace stavby" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_260219_Dum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_260217_Sklad" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stav polozek" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URS vyber audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Rekapitulace stavby" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="SO_260219_Dum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="SO_260217_Sklad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Stav polozek" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="URS vyber audit" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1846,7 +1846,7 @@
       <c r="D61" s="24" t="inlineStr"/>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče výšky ~50 mm + betonové dlaždice tl. 50 mm jako roznášecí vrstva POD terče + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie separační</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       <c r="D62" s="17" t="n"/>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>PDF řez C-C explicit composition + terasa ~30 m² odhad (rozměry z TZ ARS dům §4 terasa za op. stěnou)</t>
+          <t>PDF řez C-C explicit composition — terasa ~30 m² (rozměry z TZ ARS dům §4 terasa za op. stěnou). ŘEZ C-C: dlaždice = roznášecí vrstva POD terče (NE na terče); terče nesou dřevěnou pochozí vrstvu PSV76.002.</t>
         </is>
       </c>
       <c r="F62" s="17" t="n"/>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="G206" s="25" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H206" s="26" t="n"/>
       <c r="I206" s="26">
@@ -6949,12 +6949,12 @@
       <c r="D207" s="17" t="n"/>
       <c r="E207" s="29" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³, × 10 m³ buffer pro suti + manipulace = 6.0 m³</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="F207" s="17" t="n"/>
       <c r="G207" s="30" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H207" s="17" t="n"/>
       <c r="I207" s="17" t="n"/>
@@ -10614,14 +10614,10 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D314" s="24" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
+      <c r="D314" s="24" t="inlineStr"/>
       <c r="E314" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F314" s="23" t="inlineStr">
@@ -10642,9 +10638,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K314" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K314" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L314" s="5" t="inlineStr">
@@ -20342,12 +20338,12 @@
       <c r="E89" s="24" t="inlineStr"/>
       <c r="F89" s="24" t="inlineStr">
         <is>
-          <t>636311</t>
+          <t>564</t>
         </is>
       </c>
       <c r="G89" s="24" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaž</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrst</t>
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr">
@@ -22451,20 +22447,20 @@
           <t>PSV-76 Truhlář</t>
         </is>
       </c>
-      <c r="E153" s="24" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
-      <c r="F153" s="24" t="inlineStr"/>
+      <c r="E153" s="24" t="inlineStr"/>
+      <c r="F153" s="24" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
       <c r="G153" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový</t>
+          <t xml:space="preserve">Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném </t>
         </is>
       </c>
       <c r="H153" s="24" t="inlineStr">
         <is>
-          <t>? needs production lookup</t>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
     </row>
@@ -25448,23 +25444,23 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr"/>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>564851111</t>
+          <t>596811220, 564851111</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>636311</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>family_636311_leaf_lookup_required</t>
+          <t>family_564_leaf_lookup_required</t>
         </is>
       </c>
       <c r="I9" s="35" t="n">
@@ -25472,7 +25468,7 @@
       </c>
       <c r="J9" s="33" t="inlineStr">
         <is>
-          <t>RECONCILED_636311_terasa_na_terce</t>
+          <t>REZ_CC_CORRECTED_substructure_dlazdice_roznaseci_pod_terce</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
@@ -25483,7 +25479,7 @@
       <c r="L9" s="24" t="inlineStr"/>
       <c r="M9" s="24" t="inlineStr">
         <is>
-          <t>636311 família — betonové dlaždice NA TERČE (rektifikovatelné terče). USE busy-einstein 636311. happy-hamilton 762952004 (carpentry) DISCARDED — superseded wooden-decking assumption; frozen popis is b</t>
+          <t>ŘEZ C-C OPRAVA 2026-05-29: betonové dlaždice = ROZNÁŠECÍ vrstva POD rektifikovatelné terče (NE '636311 dlaždice na terče' — to byla chyba reconciliation). Dřevěná pochozí vrstva (prkna + dřevěný rošt,</t>
         </is>
       </c>
       <c r="N9" s="24" t="inlineStr"/>
@@ -30757,32 +30753,44 @@
       </c>
       <c r="D126" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na r</t>
-        </is>
-      </c>
-      <c r="E126" s="24" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hr</t>
+        </is>
+      </c>
+      <c r="E126" s="24" t="inlineStr"/>
       <c r="F126" s="24" t="inlineStr">
         <is>
           <t>766811111</t>
         </is>
       </c>
-      <c r="G126" s="24" t="inlineStr"/>
+      <c r="G126" s="24" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
       <c r="H126" s="24" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="I126" s="35" t="n">
         <v>0.65</v>
       </c>
-      <c r="J126" s="32" t="inlineStr"/>
+      <c r="J126" s="33" t="inlineStr">
+        <is>
+          <t>REZ_CC_CORRECTED_wood_deck_762_split_by_trade</t>
+        </is>
+      </c>
       <c r="K126" s="24" t="inlineStr"/>
-      <c r="L126" s="24" t="inlineStr"/>
-      <c r="M126" s="24" t="inlineStr"/>
+      <c r="L126" s="24" t="inlineStr">
+        <is>
+          <t>771474112</t>
+        </is>
+      </c>
+      <c r="M126" s="24" t="inlineStr">
+        <is>
+          <t>ŘEZ C-C 2026-05-29: dřevěná pochozí terasa (prkna garapa + dřevěný rošt z hranolů) → família 762 (tesařské/truhlářské konstrukce). Kód 771474112 (dlaždice domain) BYL WRONG — odstraněn (Pattern 26, ne</t>
+        </is>
+      </c>
       <c r="N126" s="24" t="inlineStr"/>
     </row>
     <row r="127">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-05-29_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-05-29_v3_final.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rekapitulace stavby" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SO_260219_Dum" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SO_260217_Sklad" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Stav polozek" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="URS vyber audit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekapitulace stavby" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_260219_Dum" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SO_260217_Sklad" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stav polozek" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URS vyber audit" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-05-29_v3_final.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_KROS_format_2026-05-29_v3_final.xlsx
@@ -1846,7 +1846,7 @@
       <c r="D61" s="24" t="inlineStr"/>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76.002 Truhlář): rektifikovatelné terče výšky ~50 mm + betonové dlaždice tl. 50 mm jako roznášecí vrstva POD terče + štěrkový podsyp 16/32 mm tl. 100 mm + hrubý podsyp 4/8 mm tl. 150 mm + geotextilie separační</t>
         </is>
       </c>
       <c r="F61" s="23" t="inlineStr">
@@ -1888,7 +1888,7 @@
       <c r="D62" s="17" t="n"/>
       <c r="E62" s="29" t="inlineStr">
         <is>
-          <t>PDF řez C-C explicit composition + terasa ~30 m² odhad (rozměry z TZ ARS dům §4 terasa za op. stěnou)</t>
+          <t>PDF řez C-C explicit composition — terasa ~30 m² (rozměry z TZ ARS dům §4 terasa za op. stěnou). ŘEZ C-C: dlaždice = roznášecí vrstva POD terče (NE na terče); terče nesou dřevěnou pochozí vrstvu PSV76.002.</t>
         </is>
       </c>
       <c r="F62" s="17" t="n"/>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="G206" s="25" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H206" s="26" t="n"/>
       <c r="I206" s="26">
@@ -6949,12 +6949,12 @@
       <c r="D207" s="17" t="n"/>
       <c r="E207" s="29" t="inlineStr">
         <is>
-          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³, × 10 m³ buffer pro suti + manipulace = 6.0 m³</t>
+          <t>průměr komín 0.50×0.50 × výška nad střechou ~2.4 m = 0.6 m³ (OPRAVA ChatGPT revize 2026-05-29: dříve 6.0 m³ = ×10 chybná inflace; skutečný objem 0.6 m³)</t>
         </is>
       </c>
       <c r="F207" s="17" t="n"/>
       <c r="G207" s="30" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="H207" s="17" t="n"/>
       <c r="I207" s="17" t="n"/>
@@ -10614,14 +10614,10 @@
           <t>K</t>
         </is>
       </c>
-      <c r="D314" s="24" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
+      <c r="D314" s="24" t="inlineStr"/>
       <c r="E314" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na rektifikovatelných terčích</t>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hranolů 50 mm na rektifikovatelných terčích (terče + podkladní skladba viz HSV1.005)</t>
         </is>
       </c>
       <c r="F314" s="23" t="inlineStr">
@@ -10642,9 +10638,9 @@
           <t>ÚRS 2026</t>
         </is>
       </c>
-      <c r="K314" s="32" t="inlineStr">
-        <is>
-          <t>? needs production lookup</t>
+      <c r="K314" s="33" t="inlineStr">
+        <is>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
       <c r="L314" s="5" t="inlineStr">
@@ -20342,12 +20338,12 @@
       <c r="E89" s="24" t="inlineStr"/>
       <c r="F89" s="24" t="inlineStr">
         <is>
-          <t>636311</t>
+          <t>564</t>
         </is>
       </c>
       <c r="G89" s="24" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaž</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrst</t>
         </is>
       </c>
       <c r="H89" s="24" t="inlineStr">
@@ -22451,20 +22447,20 @@
           <t>PSV-76 Truhlář</t>
         </is>
       </c>
-      <c r="E153" s="24" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
-      <c r="F153" s="24" t="inlineStr"/>
+      <c r="E153" s="24" t="inlineStr"/>
+      <c r="F153" s="24" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
       <c r="G153" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový</t>
+          <t xml:space="preserve">Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném </t>
         </is>
       </c>
       <c r="H153" s="24" t="inlineStr">
         <is>
-          <t>? needs production lookup</t>
+          <t>❌ MANUAL — KROS catalog lookup</t>
         </is>
       </c>
     </row>
@@ -25448,23 +25444,23 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Terasa za opěrnou stěnou: rektifikovatelné terče 50 mm + betonové dlaždice 50 mm</t>
+          <t>Terasa za opěrnou stěnou — PODKLADNÍ SKLADBA pod dřevěnou pochozí vrstvou (PSV76</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr"/>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>564851111</t>
+          <t>596811220, 564851111</t>
         </is>
       </c>
       <c r="G9" s="24" t="inlineStr">
         <is>
-          <t>636311</t>
+          <t>564</t>
         </is>
       </c>
       <c r="H9" s="24" t="inlineStr">
         <is>
-          <t>family_636311_leaf_lookup_required</t>
+          <t>family_564_leaf_lookup_required</t>
         </is>
       </c>
       <c r="I9" s="35" t="n">
@@ -25472,7 +25468,7 @@
       </c>
       <c r="J9" s="33" t="inlineStr">
         <is>
-          <t>RECONCILED_636311_terasa_na_terce</t>
+          <t>REZ_CC_CORRECTED_substructure_dlazdice_roznaseci_pod_terce</t>
         </is>
       </c>
       <c r="K9" s="24" t="inlineStr">
@@ -25483,7 +25479,7 @@
       <c r="L9" s="24" t="inlineStr"/>
       <c r="M9" s="24" t="inlineStr">
         <is>
-          <t>636311 família — betonové dlaždice NA TERČE (rektifikovatelné terče). USE busy-einstein 636311. happy-hamilton 762952004 (carpentry) DISCARDED — superseded wooden-decking assumption; frozen popis is b</t>
+          <t>ŘEZ C-C OPRAVA 2026-05-29: betonové dlaždice = ROZNÁŠECÍ vrstva POD rektifikovatelné terče (NE '636311 dlaždice na terče' — to byla chyba reconciliation). Dřevěná pochozí vrstva (prkna + dřevěný rošt,</t>
         </is>
       </c>
       <c r="N9" s="24" t="inlineStr"/>
@@ -30757,32 +30753,44 @@
       </c>
       <c r="D126" s="24" t="inlineStr">
         <is>
-          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na hliníkový rošt na r</t>
-        </is>
-      </c>
-      <c r="E126" s="24" t="inlineStr">
-        <is>
-          <t>771474112</t>
-        </is>
-      </c>
+          <t>Dřevěná terasa za opěrnou stěnou — prkna garapa 145×25 mm na dřevěném roštu z hr</t>
+        </is>
+      </c>
+      <c r="E126" s="24" t="inlineStr"/>
       <c r="F126" s="24" t="inlineStr">
         <is>
           <t>766811111</t>
         </is>
       </c>
-      <c r="G126" s="24" t="inlineStr"/>
+      <c r="G126" s="24" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
       <c r="H126" s="24" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_762_leaf_lookup_required</t>
         </is>
       </c>
       <c r="I126" s="35" t="n">
         <v>0.65</v>
       </c>
-      <c r="J126" s="32" t="inlineStr"/>
+      <c r="J126" s="33" t="inlineStr">
+        <is>
+          <t>REZ_CC_CORRECTED_wood_deck_762_split_by_trade</t>
+        </is>
+      </c>
       <c r="K126" s="24" t="inlineStr"/>
-      <c r="L126" s="24" t="inlineStr"/>
-      <c r="M126" s="24" t="inlineStr"/>
+      <c r="L126" s="24" t="inlineStr">
+        <is>
+          <t>771474112</t>
+        </is>
+      </c>
+      <c r="M126" s="24" t="inlineStr">
+        <is>
+          <t>ŘEZ C-C 2026-05-29: dřevěná pochozí terasa (prkna garapa + dřevěný rošt z hranolů) → família 762 (tesařské/truhlářské konstrukce). Kód 771474112 (dlaždice domain) BYL WRONG — odstraněn (Pattern 26, ne</t>
+        </is>
+      </c>
       <c r="N126" s="24" t="inlineStr"/>
     </row>
     <row r="127">
